--- a/artfynd/A 14815-2023 artfynd.xlsx
+++ b/artfynd/A 14815-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 14815-2023 artfynd.xlsx
+++ b/artfynd/A 14815-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>98466041</v>
       </c>
       <c r="B2" t="n">
-        <v>88476</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>416554.9614540605</v>
+        <v>416555</v>
       </c>
       <c r="R2" t="n">
-        <v>6586980.986608088</v>
+        <v>6586981</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -752,19 +747,9 @@
           <t>2021-10-06</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-10-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,7 +774,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>NVI Tyr, Rud och Kronoparken</t>
+          <t>Karlstad kommun - NVI Tyr, Rud och Kronoparken</t>
         </is>
       </c>
     </row>
@@ -798,12 +783,7 @@
         <v>98466097</v>
       </c>
       <c r="B3" t="n">
-        <v>89170</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -839,10 +819,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>416346.7042381657</v>
+        <v>416346</v>
       </c>
       <c r="R3" t="n">
-        <v>6587181.625371441</v>
+        <v>6587181</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -872,19 +852,9 @@
           <t>2021-10-05</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,7 +879,7 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>NVI Tyr, Rud och Kronoparken</t>
+          <t>Karlstad kommun - NVI Tyr, Rud och Kronoparken</t>
         </is>
       </c>
     </row>
@@ -918,12 +888,7 @@
         <v>98466094</v>
       </c>
       <c r="B4" t="n">
-        <v>5135</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -959,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>416335.6352274404</v>
+        <v>416335</v>
       </c>
       <c r="R4" t="n">
-        <v>6587188.48965151</v>
+        <v>6587188</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -992,19 +957,9 @@
           <t>2021-10-05</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-10-05</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,7 +984,7 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>NVI Tyr, Rud och Kronoparken</t>
+          <t>Karlstad kommun - NVI Tyr, Rud och Kronoparken</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 14815-2023 artfynd.xlsx
+++ b/artfynd/A 14815-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
           <t>Karlstad kommun - NVI Tyr, Rud och Kronoparken</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98466041</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
           <t>Karlstad kommun - NVI Tyr, Rud och Kronoparken</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98466097</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,8 +1002,18 @@
           <t>Karlstad kommun - NVI Tyr, Rud och Kronoparken</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98466094</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>